--- a/Configs/GameConfig/Datas/fg/#SiegeTarget-攻城职能目标.xlsx
+++ b/Configs/GameConfig/Datas/fg/#SiegeTarget-攻城职能目标.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,6 +749,69 @@
         <v>120</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>assault.purify</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>assault</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>purify</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sabotage.purify</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sabotage</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>purify</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>siege.purify</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>purify</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
